--- a/examples/本地验收报告/管理员综合督办报告.xlsx
+++ b/examples/本地验收报告/管理员综合督办报告.xlsx
@@ -24,11 +24,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'可视化看板'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'状态分布'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'风险分布'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'拖延原因'!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'拖延原因'!$A$1:$B$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'部门完成情况'!$A$1:$B$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'任务清单'!$A$1:$AF$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'任务清单'!$A$1:$AF$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'重点任务'!$A$1:$AF$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'逾期任务'!$A$1:$AF$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'逾期任务'!$A$1:$AF$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'协办任务'!$A$1:$AF$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'责任人统计'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'部门统计'!$A$1:$L$5</definedName>
@@ -315,12 +315,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'拖延原因'!$A$2</f>
+              <f>'拖延原因'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'拖延原因'!$B$2</f>
+              <f>'拖延原因'!$B$2:$B$3</f>
             </numRef>
           </val>
         </ser>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -909,9 +909,7 @@
           <t>按期完成率</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="B8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -920,7 +918,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -930,7 +928,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -940,7 +938,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1048,34 +1046,32 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>1</v>
@@ -1217,16 +1213,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -1236,13 +1232,13 @@
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>1</v>
@@ -1255,31 +1251,29 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -1365,7 +1359,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:08:09+08:00</t>
+          <t>2026-10-17T15:27:05+08:00</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1471,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1507,7 +1501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1517,7 +1511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1558,7 +1552,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1568,7 +1562,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1588,7 +1582,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1613,7 +1607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1635,15 +1629,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>尚未研判</t>
+          <t>信息不足</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>资源依赖</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B2"/>
+  <autoFilter ref="A1:B3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1710,7 +1714,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1725,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AF5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1927,18 +1931,18 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>a42ef86345fc4f7eae3675df1a4557c8</t>
+          <t>76c048b238ae486d953354a43141c24d</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>测试园区扩容</t>
+          <t>测试原生市场部交付</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>网络部</t>
+          <t>市场部</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -1954,34 +1958,54 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>办理中</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>测试初始进展</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:46+08:00</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>管理员</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟：资源依赖待核实</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>测试初始进展</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟建议：确认交付安排</t>
+        </is>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:26:54+08:00</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="n">
@@ -1992,35 +2016,35 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:46+08:00</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:46+08:00</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>管理员</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>bc8d9a8e05ac470ab75fb9e03883bc54</t>
+          <t>7799a40856de4b5693bd5315fe523083</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>测试客户走访</t>
+          <t>测试原生网络部交付</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>政企部</t>
+          <t>网络部</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -2030,7 +2054,7 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -2040,30 +2064,50 @@
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>测试初始进展</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:49+08:00</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>管理员</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟：资源依赖待核实</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>测试初始进展</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟建议：确认交付安排</t>
+        </is>
+      </c>
       <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:26:55+08:00</t>
+        </is>
+      </c>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="n">
@@ -2074,35 +2118,35 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:49+08:00</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:49+08:00</t>
         </is>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>管理员</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>d1d4938f71884c7ca66786c9c0ab7e00</t>
+          <t>74dbf809d8d04f93b4de207464b9b7fd</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>测试企业专线交付</t>
+          <t>测试原生综合部交付</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>政企部</t>
+          <t>综合部</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -2112,23 +2156,19 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>受阻</t>
+          <t>未开始</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>两处资源不足</t>
+          <t>测试初始进展</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
@@ -2136,7 +2176,7 @@
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:52+08:00</t>
+          <t>2026-10-17T15:26:51+08:00</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -2146,53 +2186,69 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟：资源依赖待核实</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>测试初始进展</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟建议：确认交付安排</t>
+        </is>
+      </c>
       <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:26:56+08:00</t>
+        </is>
+      </c>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:52+08:00</t>
+          <t>2026-10-17T15:26:51+08:00</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:51+08:00</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>管理员</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>93ef22ad874548cca48c9bc0d23e7c18</t>
+          <t>4c502519187641b98e22f03d8158d84f</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>测试渠道走访</t>
+          <t>测试原生政企部交付</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>市场部</t>
+          <t>政企部</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -2202,406 +2258,90 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>办理中</t>
+          <t>受阻</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>资源不足</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:55+08:00</t>
+          <t>2026-10-17T15:26:52.056054+08:00</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>管理员</t>
+          <t>邮件:SIM-NATIVE-1</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟：资源依赖待核实</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>资源不足</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟建议：确认交付安排</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>网络部</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:26:56+08:00</t>
+        </is>
+      </c>
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="inlineStr"/>
       <c r="AB5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:55+08:00</t>
+          <t>2026-10-17T15:26:52+08:00</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:48+08:00</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ef8955a87e994e0db9229ecdc1793382</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>测试并发事项0</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>综合部</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:08:06+08:00</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
           <t>管理员</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr"/>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr"/>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:08:06+08:00</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:08:06+08:00</t>
-        </is>
-      </c>
-      <c r="AF6" s="2" t="inlineStr">
-        <is>
-          <t>管理员</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2e1a3d8143d1433f806973c834c51104</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>测试并发事项1</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>综合部</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:08:06+08:00</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>管理员</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr"/>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:08:06+08:00</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:08:06+08:00</t>
-        </is>
-      </c>
-      <c r="AF7" s="2" t="inlineStr">
-        <is>
-          <t>管理员</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>53918a8e99e84a1db7ae6f4b88f1095a</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>测试流程材料</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>综合部</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>材料已归档</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr"/>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AF8" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>9bf1c703214a411d9fb929ae43eeeacd</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>测试取消事项</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>综合部</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr"/>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr"/>
-      <c r="Y9" s="2" t="inlineStr"/>
-      <c r="Z9" s="2" t="inlineStr"/>
-      <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AF9" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF9"/>
+  <autoFilter ref="A1:AF5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2814,12 +2554,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>d1d4938f71884c7ca66786c9c0ab7e00</t>
+          <t>4c502519187641b98e22f03d8158d84f</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>测试企业专线交付</t>
+          <t>测试原生政企部交付</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -2835,14 +2575,10 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>受阻</t>
@@ -2851,7 +2587,7 @@
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>两处资源不足</t>
+          <t>资源不足</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
@@ -2859,45 +2595,65 @@
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:52+08:00</t>
+          <t>2026-10-17T15:26:52.056054+08:00</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>管理员</t>
+          <t>邮件:SIM-NATIVE-1</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟：资源依赖待核实</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>资源不足</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟建议：确认交付安排</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>网络部</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:26:56+08:00</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:52+08:00</t>
+          <t>2026-10-17T15:26:52+08:00</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:48+08:00</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>管理员</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3112,98 +2868,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>d1d4938f71884c7ca66786c9c0ab7e00</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>测试企业专线交付</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>政企部</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>受阻</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>两处资源不足</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:52+08:00</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>管理员</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:52+08:00</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AF2"/>
+  <autoFilter ref="A1:AF1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
